--- a/evaluation/egyptian_review.xlsx
+++ b/evaluation/egyptian_review.xlsx
@@ -9323,7 +9323,7 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>أقدر أساعدك. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أساعدك. مش لاقي في حسابك حجز زي ده. لو الحجز اتعمل بالتليفون أو عن طريق شركة سياحة أو موقع حجز، قوللي رقم الحجز واسم العيلة اللي عليه وأنا أضيفه لحسابك.</t>
         </is>
       </c>
       <c r="F2" s="12" t="n"/>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>شكراً. الحجز B017220 أوضة ديلوكس من 21 أبريل 2027 لـ 26 أبريل 2027 بالسعر المرن، وانت بتلغي قبل الوصول بأكتر من 48 ساعة، فالإلغاء ببلاش. أكمّل؟</t>
+          <t>شكراً، ضفت الحجز B017220 لحسابك. الحجز B017220 أوضة ديلوكس من 21 أبريل 2027 لـ 26 أبريل 2027 بالسعر المرن، وانت بتلغي قبل الوصول بأكتر من 48 ساعة، فالإلغاء ببلاش. أكمّل؟</t>
         </is>
       </c>
       <c r="F3" s="12" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>أقدر أساعدك. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أساعدك. مش لاقي في حسابك حجز زي ده. لو الحجز اتعمل بالتليفون أو عن طريق شركة سياحة أو موقع حجز، قوللي رقم الحجز واسم العيلة اللي عليه وأنا أضيفه لحسابك.</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>شكراً. الحجز B005514 أوضة عائلية من 19 مارس 2027 لـ 23 مارس 2027 بالسعر المرن، وانت بتلغي قبل الوصول بأكتر من 48 ساعة، فالإلغاء ببلاش. أكمّل؟</t>
+          <t>شكراً، ضفت الحجز B005514 لحسابك. الحجز B005514 أوضة عائلية من 19 مارس 2027 لـ 23 مارس 2027 بالسعر المرن، وانت بتلغي قبل الوصول بأكتر من 48 ساعة، فالإلغاء ببلاش. أكمّل؟</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>أقدر أساعدك. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أساعدك. شايف في حسابك حجز B001903، الوصول يوم 11 أكتوبر. هو ده؟</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>B001903، أحمد.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>ثانية أشوف. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>ثانية أشوف. شايف في حسابك حجز B010682، الوصول يوم 15 فبراير 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>B010682، حسن.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>ثانية أشوف. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>ثانية أشوف. شايف في حسابك حجز B015579، الوصول يوم 26 يناير 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>B015579، Petit.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>ثانية أشوف. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>ثانية أشوف. شايف في حسابك حجز B001339، الوصول يوم 23 يناير 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>B001339، حداد.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>أكيد. عايز تغير إيه: التواريخ ولا نوع الأوضة ولا عدد الأفراد؟ وقوللي رقم الحجز واسم العيلة اللي عليه.</t>
+          <t>أكيد. عايز تغير إيه: التواريخ ولا نوع الأوضة ولا عدد الأفراد؟ شايف في حسابك حجز B002187، الوصول يوم 4 يونيو 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F29" s="12" t="n"/>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>رقم الحجز B002187 باسم علي، وعايز أوصل يوم 7 يونيو 2027 بدل كده.</t>
+          <t>أيوه، هو ده. عايز أوصل يوم 7 يونيو 2027 بدل كده.</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>أكيد. عايز تغير إيه: التواريخ ولا نوع الأوضة ولا عدد الأفراد؟ وقوللي رقم الحجز واسم العيلة اللي عليه.</t>
+          <t>أكيد. عايز تغير إيه: التواريخ ولا نوع الأوضة ولا عدد الأفراد؟ شايف في حسابك حجز B001670، الوصول يوم 7 أغسطس 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F32" s="12" t="n"/>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>رقم الحجز B001670 باسم الغامدي، وعايز أوصل يوم 14 أغسطس 2027 بدل كده.</t>
+          <t>أيوه، هو ده. عايز أوصل يوم 14 أغسطس 2027 بدل كده.</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>أكيد. عايز تغير إيه: التواريخ ولا نوع الأوضة ولا عدد الأفراد؟ وقوللي رقم الحجز واسم العيلة اللي عليه.</t>
+          <t>أكيد. عايز تغير إيه: التواريخ ولا نوع الأوضة ولا عدد الأفراد؟ شايف في حسابك حجز B005298، الوصول يوم 16 يوليو 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F35" s="12" t="n"/>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>رقم الحجز B005298 باسم أحمد، وعايز أوصل يوم 30 يوليو 2027 بدل كده.</t>
+          <t>أيوه، هو ده. عايز أوصل يوم 30 يوليو 2027 بدل كده.</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>أقدر أطلبهولك. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أطلبهولك. شايف في حسابك حجز B008190، الوصول يوم 21 فبراير 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F38" s="12" t="n"/>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>B008190، Thomas.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>أقدر أطلبهولك. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أطلبهولك. شايف في حسابك حجز B009399، الوصول يوم 28 ديسمبر. هو ده؟</t>
         </is>
       </c>
       <c r="F41" s="12" t="n"/>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>B009399، يوسف.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>أقدر أطلبهولك. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أطلبهولك. شايف في حسابك حجز B002927، الوصول يوم 1 أبريل 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F44" s="12" t="n"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>B002927، علي.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>أقدر أطلبلك تغيير نوع الأوضة. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أطلبلك تغيير نوع الأوضة. شايف في حسابك حجز B013440، الوصول يوم 2 نوفمبر. هو ده؟</t>
         </is>
       </c>
       <c r="F47" s="12" t="n"/>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>B013440، الشمري.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>أقدر أطلبلك تغيير نوع الأوضة. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أطلبلك تغيير نوع الأوضة. شايف في حسابك حجز B004618، الوصول يوم 26 ديسمبر. هو ده؟</t>
         </is>
       </c>
       <c r="F50" s="12" t="n"/>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>B004618، Kuznetsov.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>أقدر أطلبلك تغيير نوع الأوضة. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أطلبلك تغيير نوع الأوضة. شايف في حسابك حجز B012064، الوصول يوم 11 يناير 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F53" s="12" t="n"/>
@@ -10774,7 +10774,7 @@
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>B012064، سعيد.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>أشوفلك الأوضة تساع ولا لأ. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أشوفلك الأوضة تساع ولا لأ. شايف في حسابك حجز B008918، الوصول يوم 31 مارس 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F56" s="12" t="n"/>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>B008918، محمود. هنبقى 3 أفراد.</t>
+          <t>أيوه، هو ده. هنبقى 3 أفراد.</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>أشوفلك الأوضة تساع ولا لأ. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أشوفلك الأوضة تساع ولا لأ. شايف في حسابك حجز B007487، الوصول يوم 7 أكتوبر. هو ده؟</t>
         </is>
       </c>
       <c r="F59" s="12" t="n"/>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>B007487، الزهراني. هنبقى 4 أفراد.</t>
+          <t>أيوه، هو ده. هنبقى 4 أفراد.</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>أشوفلك الأوضة تساع ولا لأ. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أشوفلك الأوضة تساع ولا لأ. شايف في حسابك حجز B004333، الوصول يوم 4 مايو 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F62" s="12" t="n"/>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>B004333، جمال. هنبقى 4 أفراد.</t>
+          <t>أيوه، هو ده. هنبقى 4 أفراد.</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>أكيد أطلبهولك. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أكيد أطلبهولك. شايف في حسابك حجز B005504، الوصول يوم 26 نوفمبر. هو ده؟</t>
         </is>
       </c>
       <c r="F65" s="12" t="n"/>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>B005504، Taylor. ينفع أخرج يوم 11 ديسمبر؟</t>
+          <t>أيوه، هو ده. ينفع أخرج يوم 11 ديسمبر؟</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>أكيد أطلبهولك. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أكيد أطلبهولك. شايف في حسابك حجز B007272، الوصول يوم 24 مايو 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F68" s="12" t="n"/>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>B007272، النعيمي. ينفع أخرج يوم 5 يونيو 2027؟</t>
+          <t>أيوه، هو ده. ينفع أخرج يوم 5 يونيو 2027؟</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>أكيد أطلبهولك. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أكيد أطلبهولك. شايف في حسابك حجز B000671، الوصول يوم 24 مايو 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F71" s="12" t="n"/>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>B000671، العجمي. ينفع أخرج يوم 2 يونيو 2027؟</t>
+          <t>أيوه، هو ده. ينفع أخرج يوم 2 يونيو 2027؟</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>آسفين إن ده حصل. قوللي إيه اللي حصل وادّيني رقم الحجز.</t>
+          <t>آسفين إن ده حصل. قوللي إيه اللي حصل. شايف في حسابك حجز B010283، الوصول يوم 10 سبتمبر. هو ده؟</t>
         </is>
       </c>
       <c r="F83" s="12" t="n"/>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>B010283. استنينا أربعين دقيقة ومحدش جه للترابيزة.</t>
+          <t>أيوه، هو ده. استنينا أربعين دقيقة ومحدش جه للترابيزة.</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>آسفين إن ده حصل. قوللي إيه اللي حصل وادّيني رقم الحجز.</t>
+          <t>آسفين إن ده حصل. قوللي إيه اللي حصل. شايف في حسابك حجز B018133، الوصول يوم 12 سبتمبر. هو ده؟</t>
         </is>
       </c>
       <c r="F86" s="12" t="n"/>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>B018133. استنينا أربعين دقيقة ومحدش جه للترابيزة.</t>
+          <t>أيوه، هو ده. استنينا أربعين دقيقة ومحدش جه للترابيزة.</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>آسفين إن ده حصل. قوللي إيه اللي حصل وادّيني رقم الحجز.</t>
+          <t>آسفين إن ده حصل. قوللي إيه اللي حصل. مش لاقي في حسابك حجز زي ده. لو الحجز اتعمل بالتليفون أو عن طريق شركة سياحة أو موقع حجز، قوللي رقم الحجز واسم العيلة اللي عليه وأنا أضيفه لحسابك.</t>
         </is>
       </c>
       <c r="F89" s="12" t="n"/>
@@ -11782,12 +11782,12 @@
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>B002730. استنينا أربعين دقيقة ومحدش جه للترابيزة.</t>
+          <t>B002730، جمال. استنينا أربعين دقيقة ومحدش جه للترابيزة.</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>شكراً. سجلت شكوى رسمية على الحجز B002730 بخصوص خدمة الفطار، وهتتراجع والفندق هيتابع معاك، ولو مش راضي عن النتيجة ممكن تتصعّد للإدارة.</t>
+          <t>شكراً، ضفت الحجز B002730 لحسابك. سجلت شكوى رسمية على الحجز B002730 بخصوص خدمة الفطار، وهتتراجع والفندق هيتابع معاك، ولو مش راضي عن النتيجة ممكن تتصعّد للإدارة.</t>
         </is>
       </c>
       <c r="F90" s="12" t="n"/>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>أقدر أسجله للمراجعة. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أسجله للمراجعة. شايف في حسابك حجز B016506، الوصول يوم 20 أغسطس. هو ده؟</t>
         </is>
       </c>
       <c r="F92" s="12" t="n"/>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>B016506، منصور.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>أقدر أسجله للمراجعة. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أسجله للمراجعة. شايف في حسابك حجز B019453، الوصول يوم 9 سبتمبر. هو ده؟</t>
         </is>
       </c>
       <c r="F95" s="12" t="n"/>
@@ -11950,7 +11950,7 @@
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>B019453، المهيري.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>أقدر أسجله للمراجعة. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أسجله للمراجعة. مش لاقي في حسابك حجز زي ده. لو الحجز اتعمل بالتليفون أو عن طريق شركة سياحة أو موقع حجز، قوللي رقم الحجز واسم العيلة اللي عليه وأنا أضيفه لحسابك.</t>
         </is>
       </c>
       <c r="F98" s="12" t="n"/>
@@ -12039,7 +12039,7 @@
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>الحجز B015380 كان جناح من 8 سبتمبر لـ 19 سبتمبر، وإجماليه 261,748.85 جنيه. سجلت المبلغ اللي معترض عليه كشكوى فاتورة، وخدمة العملاء هتراجع العملية وتكلمك بالنتيجة.</t>
+          <t>شكراً، ضفت الحجز B015380 لحسابك. الحجز B015380 كان جناح من 8 سبتمبر لـ 19 سبتمبر، وإجماليه 261,748.85 جنيه. سجلت المبلغ اللي معترض عليه كشكوى فاتورة، وخدمة العملاء هتراجع العملية وتكلمك بالنتيجة.</t>
         </is>
       </c>
       <c r="F99" s="12" t="n"/>
@@ -12347,7 +12347,7 @@
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>أكيد. الشكاوى بعد الخروج خدمة العملاء بتتابعها. رقم الحجز كام؟</t>
+          <t>أكيد. الشكاوى بعد الخروج خدمة العملاء بتتابعها. شايف في حسابك حجز B015664، الوصول يوم 30 أغسطس. هو ده؟</t>
         </is>
       </c>
       <c r="F110" s="12" t="n"/>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>B015664. الأوضة ماكانتش بتتنضف طول الإقامة.</t>
+          <t>أيوه، هو ده. الأوضة ماكانتش بتتنضف طول الإقامة.</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>أكيد. الشكاوى بعد الخروج خدمة العملاء بتتابعها. رقم الحجز كام؟</t>
+          <t>أكيد. الشكاوى بعد الخروج خدمة العملاء بتتابعها. مش لاقي في حسابك حجز زي ده. لو الحجز اتعمل بالتليفون أو عن طريق شركة سياحة أو موقع حجز، قوللي رقم الحجز واسم العيلة اللي عليه وأنا أضيفه لحسابك.</t>
         </is>
       </c>
       <c r="F113" s="12" t="n"/>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>B014672. الأوضة ماكانتش بتتنضف طول الإقامة.</t>
+          <t>B014672، جمال. الأوضة ماكانتش بتتنضف طول الإقامة.</t>
         </is>
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>شكراً. سجلت شكوى على الحجز B014672، أوضة عائلية من 3 سبتمبر لـ 17 سبتمبر، بخصوص التنضيف. خدمة العملاء هتراجعها وتتابع معاك.</t>
+          <t>شكراً، ضفت الحجز B014672 لحسابك. سجلت شكوى على الحجز B014672، أوضة عائلية من 3 سبتمبر لـ 17 سبتمبر، بخصوص التنضيف. خدمة العملاء هتراجعها وتتابع معاك.</t>
         </is>
       </c>
       <c r="F114" s="12" t="n"/>
@@ -12515,7 +12515,7 @@
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>أكيد. الشكاوى بعد الخروج خدمة العملاء بتتابعها. رقم الحجز كام؟</t>
+          <t>أكيد. الشكاوى بعد الخروج خدمة العملاء بتتابعها. شايف في حسابك حجز B008156، الوصول يوم 6 سبتمبر. هو ده؟</t>
         </is>
       </c>
       <c r="F116" s="12" t="n"/>
@@ -12538,7 +12538,7 @@
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>B008156. الأوضة ماكانتش بتتنضف طول الإقامة.</t>
+          <t>أيوه، هو ده. الأوضة ماكانتش بتتنضف طول الإقامة.</t>
         </is>
       </c>
       <c r="E117" s="9" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
-          <t>أيوة، الفندق يقدر يرتبلك أكل نباتي في الفطار وخدمة الأوض. رقم الحجز كام عشان أسجله؟</t>
+          <t>أيوة، الفندق يقدر يرتبلك أكل نباتي في الفطار وخدمة الأوض. شايف في حسابك حجز B008870، الوصول يوم 16 فبراير 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F119" s="12" t="n"/>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>B008870.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>أيوة، الفندق يقدر يرتبلك أكل نباتي في الفطار وخدمة الأوض. رقم الحجز كام عشان أسجله؟</t>
+          <t>أيوة، الفندق يقدر يرتبلك أكل نباتي في الفطار وخدمة الأوض. شايف في حسابك حجز B001255، الوصول يوم 15 فبراير 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F122" s="12" t="n"/>
@@ -12706,7 +12706,7 @@
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>B001255.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>أيوة، الفندق يقدر يرتبلك أكل نباتي في الفطار وخدمة الأوض. رقم الحجز كام عشان أسجله؟</t>
+          <t>أيوة، الفندق يقدر يرتبلك أكل نباتي في الفطار وخدمة الأوض. شايف في حسابك حجز B009858، الوصول يوم 10 أغسطس 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F125" s="12" t="n"/>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>B009858.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E126" s="9" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>أقدر أضيفها كطلب. رقم الحجز كام؟</t>
+          <t>أقدر أضيفها كطلب. شايف في حسابك حجز B000972، الوصول يوم 7 مارس 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F128" s="12" t="n"/>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>B000972.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E129" s="9" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="E131" s="9" t="inlineStr">
         <is>
-          <t>أقدر أضيفها كطلب. رقم الحجز كام؟</t>
+          <t>أقدر أضيفها كطلب. شايف في حسابك حجز B000725، الوصول يوم 2 مايو 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F131" s="12" t="n"/>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>B000725.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E132" s="9" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="E134" s="9" t="inlineStr">
         <is>
-          <t>أقدر أضيفها كطلب. رقم الحجز كام؟</t>
+          <t>أقدر أضيفها كطلب. شايف في حسابك حجز B012282، الوصول يوم 27 أبريل 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F134" s="12" t="n"/>
@@ -13042,7 +13042,7 @@
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>B012282.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E135" s="9" t="inlineStr">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
-          <t>مبروك! الفندق يقدر يزيّن الأوضة ويعمل ترتيبات خاصة عند الطلب، وبعض الترتيبات ممكن يبقى عليها رسوم. رقم الحجز كام؟</t>
+          <t>مبروك! الفندق يقدر يزيّن الأوضة ويعمل ترتيبات خاصة عند الطلب، وبعض الترتيبات ممكن يبقى عليها رسوم. شايف في حسابك حجز B006433، الوصول يوم 29 أكتوبر. هو ده؟</t>
         </is>
       </c>
       <c r="F137" s="12" t="n"/>
@@ -13126,7 +13126,7 @@
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>B006433.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>مبروك! الفندق يقدر يزيّن الأوضة ويعمل ترتيبات خاصة عند الطلب، وبعض الترتيبات ممكن يبقى عليها رسوم. رقم الحجز كام؟</t>
+          <t>مبروك! الفندق يقدر يزيّن الأوضة ويعمل ترتيبات خاصة عند الطلب، وبعض الترتيبات ممكن يبقى عليها رسوم. شايف في حسابك حجز B000387، الوصول يوم 18 ديسمبر. هو ده؟</t>
         </is>
       </c>
       <c r="F140" s="12" t="n"/>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>B000387.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E141" s="9" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
-          <t>مبروك! الفندق يقدر يزيّن الأوضة ويعمل ترتيبات خاصة عند الطلب، وبعض الترتيبات ممكن يبقى عليها رسوم. رقم الحجز كام؟</t>
+          <t>مبروك! الفندق يقدر يزيّن الأوضة ويعمل ترتيبات خاصة عند الطلب، وبعض الترتيبات ممكن يبقى عليها رسوم. مش لاقي في حسابك حجز زي ده. لو الحجز اتعمل بالتليفون أو عن طريق شركة سياحة أو موقع حجز، قوللي رقم الحجز واسم العيلة اللي عليه وأنا أضيفه لحسابك.</t>
         </is>
       </c>
       <c r="F143" s="12" t="n"/>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>B010455.</t>
+          <t>B010455، جمال.</t>
         </is>
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>ضفت طلب الاحتفال بعيد الجواز على الحجز B010455 لإقامتك اللي بتبدأ يوم 16 مايو 2027. الفندق هيكلمك يأكدلك إيه اللي ينفع يترتب وتكلفته.</t>
+          <t>شكراً، ضفت الحجز B010455 لحسابك. ضفت طلب الاحتفال بعيد الجواز على الحجز B010455 لإقامتك اللي بتبدأ يوم 16 مايو 2027. الفندق هيكلمك يأكدلك إيه اللي ينفع يترتب وتكلفته.</t>
         </is>
       </c>
       <c r="F144" s="12" t="n"/>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>ثانية أشوف الحجز. رقمه كام؟</t>
+          <t>ثانية أشوف الحجز. مش لاقي في حسابك حجز زي ده. لو الحجز اتعمل بالتليفون أو عن طريق شركة سياحة أو موقع حجز، قوللي رقم الحجز واسم العيلة اللي عليه وأنا أضيفه لحسابك.</t>
         </is>
       </c>
       <c r="F146" s="12" t="n"/>
@@ -13378,12 +13378,12 @@
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>B003387.</t>
+          <t>B003387، حامد.</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>الحجز B003387 أوضة عائلية من 3 مايو 2027 لـ 17 مايو 2027، وعدد الأفراد 2، وبتاخد لحد 4 والأطفال محسوبين، يعني فرد زيادة ينفع. السرير الإضافي بـ 2,500 جنيه في الليلة على حسب المتاح. أطلبهولك؟</t>
+          <t>شكراً، ضفت الحجز B003387 لحسابك. الحجز B003387 أوضة عائلية من 3 مايو 2027 لـ 17 مايو 2027، وعدد الأفراد 2، وبتاخد لحد 4 والأطفال محسوبين، يعني فرد زيادة ينفع. السرير الإضافي بـ 2,500 جنيه في الليلة على حسب المتاح. أطلبهولك؟</t>
         </is>
       </c>
       <c r="F147" s="12" t="n"/>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>ثانية أشوف الحجز. رقمه كام؟</t>
+          <t>ثانية أشوف الحجز. شايف في حسابك حجز B015557، الوصول يوم 20 يونيو 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F149" s="12" t="n"/>
@@ -13462,7 +13462,7 @@
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>B015557.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
-          <t>ثانية أشوف الحجز. رقمه كام؟</t>
+          <t>ثانية أشوف الحجز. مش لاقي في حسابك حجز زي ده. لو الحجز اتعمل بالتليفون أو عن طريق شركة سياحة أو موقع حجز، قوللي رقم الحجز واسم العيلة اللي عليه وأنا أضيفه لحسابك.</t>
         </is>
       </c>
       <c r="F152" s="12" t="n"/>
@@ -13546,12 +13546,12 @@
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>B003700.</t>
+          <t>B003700، فاروق.</t>
         </is>
       </c>
       <c r="E153" s="9" t="inlineStr">
         <is>
-          <t>الحجز B003700 أوضة بسريرين من 23 يونيو 2027 لـ 1 يوليو 2027، وعدد الأفراد 2، وبتاخد لحد 2 بس والأطفال محسوبين، يعني طفل زيادة هيعدّي السعة حتى بسرير إضافي. أوضة ديلوكس بتاخد لحد 3 وسعرها الأساسي 12,000 جنيه في الليلة. أطلبلك تغيير لـ أوضة ديلوكس على حسب المتاح؟</t>
+          <t>شكراً، ضفت الحجز B003700 لحسابك. الحجز B003700 أوضة بسريرين من 23 يونيو 2027 لـ 1 يوليو 2027، وعدد الأفراد 2، وبتاخد لحد 2 بس والأطفال محسوبين، يعني طفل زيادة هيعدّي السعة حتى بسرير إضافي. أوضة ديلوكس بتاخد لحد 3 وسعرها الأساسي 12,000 جنيه في الليلة. أطلبلك تغيير لـ أوضة ديلوكس على حسب المتاح؟</t>
         </is>
       </c>
       <c r="F153" s="12" t="n"/>
@@ -13607,7 +13607,7 @@
       </c>
       <c r="E155" s="9" t="inlineStr">
         <is>
-          <t>شكراً إنك بلغتنا. رقم الحجز كام؟</t>
+          <t>شكراً إنك بلغتنا. شايف في حسابك حجز B012803، الوصول يوم 30 مايو 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F155" s="12" t="n"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>B012803.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E156" s="9" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="E158" s="9" t="inlineStr">
         <is>
-          <t>شكراً إنك بلغتنا. رقم الحجز كام؟</t>
+          <t>شكراً إنك بلغتنا. شايف في حسابك حجز B011472، الوصول يوم 4 نوفمبر. هو ده؟</t>
         </is>
       </c>
       <c r="F158" s="12" t="n"/>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>B011472.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E159" s="9" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="E161" s="9" t="inlineStr">
         <is>
-          <t>شكراً إنك بلغتنا. رقم الحجز كام؟</t>
+          <t>شكراً إنك بلغتنا. مش لاقي في حسابك حجز زي ده. لو الحجز اتعمل بالتليفون أو عن طريق شركة سياحة أو موقع حجز، قوللي رقم الحجز واسم العيلة اللي عليه وأنا أضيفه لحسابك.</t>
         </is>
       </c>
       <c r="F161" s="12" t="n"/>
@@ -13798,12 +13798,12 @@
       </c>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>B002314.</t>
+          <t>B002314، Smith.</t>
         </is>
       </c>
       <c r="E162" s="9" t="inlineStr">
         <is>
-          <t>الحجز B002314 بيبدأ يوم 27 نوفمبر. الحجز بيفضل محجوز لحد 11:59 بالليل يوم الوصول، فضفت عليه ملاحظة إنك هتوصل متأخر عشان مايتسجلش عدم حضور. الاستقبال شغال 24 ساعة ويقدر يعملك check-in في أي وقت.</t>
+          <t>شكراً، ضفت الحجز B002314 لحسابك. الحجز B002314 بيبدأ يوم 27 نوفمبر. الحجز بيفضل محجوز لحد 11:59 بالليل يوم الوصول، فضفت عليه ملاحظة إنك هتوصل متأخر عشان مايتسجلش عدم حضور. الاستقبال شغال 24 ساعة ويقدر يعملك check-in في أي وقت.</t>
         </is>
       </c>
       <c r="F162" s="12" t="n"/>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="E191" s="9" t="inlineStr">
         <is>
-          <t>ثانية أشوف. رقم الحجز كام؟</t>
+          <t>ثانية أشوف. شايف في حسابك حجز B009291، الوصول يوم 5 يونيو 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F191" s="12" t="n"/>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="D192" s="9" t="inlineStr">
         <is>
-          <t>B009291.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E192" s="9" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="E194" s="9" t="inlineStr">
         <is>
-          <t>ثانية أشوف. رقم الحجز كام؟</t>
+          <t>ثانية أشوف. شايف في حسابك حجز B018991، الوصول يوم 5 مايو 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F194" s="12" t="n"/>
@@ -14722,7 +14722,7 @@
       </c>
       <c r="D195" s="9" t="inlineStr">
         <is>
-          <t>B018991.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E195" s="9" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="E197" s="9" t="inlineStr">
         <is>
-          <t>ثانية أشوف. رقم الحجز كام؟</t>
+          <t>ثانية أشوف. شايف في حسابك حجز B008767، الوصول يوم 31 مايو 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F197" s="12" t="n"/>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="D198" s="9" t="inlineStr">
         <is>
-          <t>B008767.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E198" s="9" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="E200" s="9" t="inlineStr">
         <is>
-          <t>أقدر أشوفلك. رقم العضوية كام؟</t>
+          <t>أقدر أشوفلك. حسابك عليه العضوية LM00084. أشوفهالك؟</t>
         </is>
       </c>
       <c r="F200" s="12" t="n"/>
@@ -14890,7 +14890,7 @@
       </c>
       <c r="D201" s="9" t="inlineStr">
         <is>
-          <t>LM00084.</t>
+          <t>أيوه لو سمحت.</t>
         </is>
       </c>
       <c r="E201" s="9" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="E203" s="9" t="inlineStr">
         <is>
-          <t>أقدر أشوفلك. رقم العضوية كام؟</t>
+          <t>أقدر أشوفلك. حسابك عليه العضوية LM00011. أشوفهالك؟</t>
         </is>
       </c>
       <c r="F203" s="12" t="n"/>
@@ -14974,7 +14974,7 @@
       </c>
       <c r="D204" s="9" t="inlineStr">
         <is>
-          <t>LM00011.</t>
+          <t>أيوه لو سمحت.</t>
         </is>
       </c>
       <c r="E204" s="9" t="inlineStr">
@@ -15035,7 +15035,7 @@
       </c>
       <c r="E206" s="9" t="inlineStr">
         <is>
-          <t>أقدر أشوفلك. رقم العضوية كام؟</t>
+          <t>أقدر أشوفلك. حسابك عليه العضوية LM00020. أشوفهالك؟</t>
         </is>
       </c>
       <c r="F206" s="12" t="n"/>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="D207" s="9" t="inlineStr">
         <is>
-          <t>LM00020.</t>
+          <t>أيوه لو سمحت.</t>
         </is>
       </c>
       <c r="E207" s="9" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="D228" s="9" t="inlineStr">
         <is>
-          <t>هحتاج فطار نباتي، والحجز رقم B017810.</t>
+          <t>هحتاج فطار نباتي.</t>
         </is>
       </c>
       <c r="E228" s="9" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>هحتاج فطار نباتي، والحجز رقم B019535.</t>
+          <t>هحتاج فطار نباتي.</t>
         </is>
       </c>
       <c r="E231" s="9" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="D234" s="9" t="inlineStr">
         <is>
-          <t>هحتاج فطار نباتي، والحجز رقم B016819.</t>
+          <t>هحتاج فطار نباتي.</t>
         </is>
       </c>
       <c r="E234" s="9" t="inlineStr">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>احجزلي جلسة لو سمحت. رقم الحجز B000408.</t>
+          <t>احجزلي جلسة لو سمحت.</t>
         </is>
       </c>
       <c r="E237" s="9" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="D240" s="9" t="inlineStr">
         <is>
-          <t>احجزلي جلسة لو سمحت. رقم الحجز B010825.</t>
+          <t>احجزلي جلسة لو سمحت.</t>
         </is>
       </c>
       <c r="E240" s="9" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
-          <t>احجزلي جلسة لو سمحت. رقم الحجز B004273.</t>
+          <t>احجزلي جلسة لو سمحت.</t>
         </is>
       </c>
       <c r="E243" s="9" t="inlineStr">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>أقدر أشوفلك. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أشوفلك. شايف في حسابك حجز B011801، الوصول يوم 9 يونيو 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F284" s="12" t="n"/>
@@ -17242,7 +17242,7 @@
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>B011801، الشمري.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
@@ -17303,7 +17303,7 @@
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>أقدر أشوفلك. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أشوفلك. شايف في حسابك حجز B011049، الوصول يوم 8 أبريل 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F287" s="12" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>B011049، الشمري.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>أقدر أشوفلك. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>أقدر أشوفلك. شايف في حسابك حجز B005706، الوصول يوم 26 يوليو 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F290" s="12" t="n"/>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>B005706، المهيري.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>ثانية أشوف. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>ثانية أشوف. شايف في حسابك حجز B003522، الوصول يوم 29 ديسمبر. هو ده؟</t>
         </is>
       </c>
       <c r="F308" s="12" t="n"/>
@@ -17914,7 +17914,7 @@
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>B003522، إبراهيم.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>ثانية أشوف. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>ثانية أشوف. مش لاقي في حسابك حجز زي ده. لو الحجز اتعمل بالتليفون أو عن طريق شركة سياحة أو موقع حجز، قوللي رقم الحجز واسم العيلة اللي عليه وأنا أضيفه لحسابك.</t>
         </is>
       </c>
       <c r="F311" s="12" t="n"/>
@@ -18003,7 +18003,7 @@
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>أيوة، الحجز B002885 مدفوع كله: 7,528.45 جنيه.</t>
+          <t>شكراً، ضفت الحجز B002885 لحسابك. أيوة، الحجز B002885 مدفوع كله: 7,528.45 جنيه.</t>
         </is>
       </c>
       <c r="F312" s="12" t="n"/>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>ثانية أشوف. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>ثانية أشوف. شايف في حسابك حجز B004418، الوصول يوم 5 أبريل 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F314" s="12" t="n"/>
@@ -18082,7 +18082,7 @@
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>B004418، حامد.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
@@ -18143,7 +18143,7 @@
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>آسفين على كده. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>آسفين على كده. شايف في حسابك حجز B013372، الوصول يوم 16 أبريل 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F317" s="12" t="n"/>
@@ -18166,7 +18166,7 @@
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>B013372، العجمي. الأوضة لسه محجوزالي؟</t>
+          <t>أيوه، هو ده. الأوضة لسه محجوزالي؟</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
@@ -18227,7 +18227,7 @@
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>آسفين على كده. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>آسفين على كده. شايف في حسابك حجز B012826، الوصول يوم 19 نوفمبر. هو ده؟</t>
         </is>
       </c>
       <c r="F320" s="12" t="n"/>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>B012826، الزهراني. الأوضة لسه محجوزالي؟</t>
+          <t>أيوه، هو ده. الأوضة لسه محجوزالي؟</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
@@ -18311,7 +18311,7 @@
       </c>
       <c r="E323" s="9" t="inlineStr">
         <is>
-          <t>آسفين على كده. رقم الحجز كام واسم العيلة اللي عليه؟</t>
+          <t>آسفين على كده. شايف في حسابك حجز B009382، الوصول يوم 5 ديسمبر. هو ده؟</t>
         </is>
       </c>
       <c r="F323" s="12" t="n"/>
@@ -18334,7 +18334,7 @@
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>B009382، Fischer. الأوضة لسه محجوزالي؟</t>
+          <t>أيوه، هو ده. الأوضة لسه محجوزالي؟</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>الأوضة اللي بسريرين 3 ليالي إجماليها 25,500 جنيه. محتاج اسمك بالكامل وبيانات التواصل عشان أكمل الحجز، وشروط الدفع بتعتمد على الحجز وهأكدهالك قبل ما يتخصم أي حاجة.</t>
+          <t>الأوضة اللي بسريرين 3 ليالي إجماليها 25,500 جنيه. هحجزهالك على حسابك بالسعر المرن: تدفع أول ليلة، 8,500 جنيه، بلينك دفع، والباقي في الفندق. أكمّل؟</t>
         </is>
       </c>
       <c r="F328" s="12" t="n"/>
@@ -18474,12 +18474,12 @@
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>تمام، اسمي على الحساب اللي عندكم.</t>
+          <t>أيوه كمّل.</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
         <is>
-          <t>شكراً، ببعت الحجز دلوقتي وهيوصلك تأكيد تحتفظ بيه. محتاج أي حاجة تانية؟</t>
+          <t>تمام — الحجز اتعمل ولينك الدفع اتبعت على إيميلك. الأوضة متحجزالك 24 ساعة لحد ما العربون يتدفع. محتاج أي حاجة تانية؟</t>
         </is>
       </c>
       <c r="F329" s="12" t="n"/>
@@ -18927,7 +18927,7 @@
       </c>
       <c r="E345" s="9" t="inlineStr">
         <is>
-          <t>مالقيتش حجز بالرقم ده. ممكن تتأكد من الرقم، أو تقولي الاسم اللي الحجز باسمه وتاريخ الوصول عشان أدور بطريقة تانية؟</t>
+          <t>مالقيتش حجز بالرقم ده، ومفيش حجز زيه في حسابك. ممكن تتأكد من الرقم؟ لو الحجز اتعمل بالتليفون أو عن طريق شركة أو باسم حد تاني، أقدر أضيفه لحسابك برقم الحجز الصح واسم العيلة اللي عليه.</t>
         </is>
       </c>
       <c r="F345" s="12" t="n"/>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="E346" s="9" t="inlineStr">
         <is>
-          <t>شكراً. محتاج اسمها بالكامل زي ما هو مكتوب في الحجز عشان أدور بالاسم والتاريخ.</t>
+          <t>يبقى محتاج رقم الحجز الصح واسم عيلتها زي ما هو مكتوب في الحجز، وأنا أضيفه لحسابك.</t>
         </is>
       </c>
       <c r="F346" s="12" t="n"/>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="E348" s="9" t="inlineStr">
         <is>
-          <t>أقدر أطلبهولك. ممكن رقم الحجز عشان ألاقيه؟</t>
+          <t>أقدر أطلبهولك. شايف في حسابك حجز B018584، الوصول يوم 4 مارس 2027. هو ده؟</t>
         </is>
       </c>
       <c r="F348" s="12" t="n"/>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="D349" s="9" t="inlineStr">
         <is>
-          <t>الرقم B018584.</t>
+          <t>أيوه، هو ده.</t>
         </is>
       </c>
       <c r="E349" s="9" t="inlineStr">

--- a/evaluation/egyptian_review.xlsx
+++ b/evaluation/egyptian_review.xlsx
@@ -557,11 +557,11 @@
     <row r="11" ht="15" customHeight="1" s="7">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>FAQ_Answers (215)</t>
+          <t>FAQ_Answers (218)</t>
         </is>
       </c>
       <c r="B11" s="9">
-        <f>COUNTIF(FAQ_Answers!H2:H216,"تمام")&amp;" / "&amp;COUNTIF(FAQ_Answers!H2:H216,"محتاج تعديل")&amp;" / "&amp;COUNTIF(FAQ_Answers!H2:H216,"مش متأكد")&amp;" / "&amp;COUNTBLANK(FAQ_Answers!H2:H216)</f>
+        <f>COUNTIF(FAQ_Answers!H2:H219,"تمام")&amp;" / "&amp;COUNTIF(FAQ_Answers!H2:H219,"محتاج تعديل")&amp;" / "&amp;COUNTIF(FAQ_Answers!H2:H219,"مش متأكد")&amp;" / "&amp;COUNTBLANK(FAQ_Answers!H2:H219)</f>
         <v/>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K216"/>
+  <dimension ref="A1:K219"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="6" min="1" max="1"/>
@@ -9227,10 +9227,127 @@
       <c r="J216" s="12" t="n"/>
       <c r="K216" s="12" t="n"/>
     </row>
+    <row r="217">
+      <c r="A217" s="9" t="inlineStr">
+        <is>
+          <t>E216</t>
+        </is>
+      </c>
+      <c r="B217" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C217" s="9" t="inlineStr">
+        <is>
+          <t>INT034</t>
+        </is>
+      </c>
+      <c r="D217" s="9" t="inlineStr">
+        <is>
+          <t>FAQ3986</t>
+        </is>
+      </c>
+      <c r="E217" s="9" t="inlineStr">
+        <is>
+          <t>إزاي أعمل حساب على الموقع بتاعكم؟</t>
+        </is>
+      </c>
+      <c r="F217" s="9" t="inlineStr">
+        <is>
+          <t>سجّل في موقع الفندق بإيميلك وباسورد، وهيوصلك كود من 6 أرقام تأكّد بيه الإيميل: شغال مرة واحدة لمدة 10 دقايق، وليك 5 محاولات بالكتير. وبعد ما تعمل لوجين تقدر تحجز وتتابع حجوزاتك.</t>
+        </is>
+      </c>
+      <c r="G217" s="9" t="inlineStr">
+        <is>
+          <t>سجّل في موقع الفندق ببريدك الإلكتروني وكلمة مرور، وسنرسل إليك رمزاً من 6 أرقام لتأكيد البريد: يُستخدم مرة واحدة خلال 10 دقائق، مع 5 محاولات كحد أقصى. وبعد تسجيل الدخول يمكنك الحجز وإدارة حجوزاتك.</t>
+        </is>
+      </c>
+      <c r="H217" s="12" t="n"/>
+      <c r="I217" s="12" t="n"/>
+      <c r="J217" s="12" t="n"/>
+      <c r="K217" s="12" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="9" t="inlineStr">
+        <is>
+          <t>E217</t>
+        </is>
+      </c>
+      <c r="B218" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C218" s="9" t="inlineStr">
+        <is>
+          <t>INT034</t>
+        </is>
+      </c>
+      <c r="D218" s="9" t="inlineStr">
+        <is>
+          <t>FAQ3991</t>
+        </is>
+      </c>
+      <c r="E218" s="9" t="inlineStr">
+        <is>
+          <t>نسيت الباسورد بتاعي، أعمل إيه؟</t>
+        </is>
+      </c>
+      <c r="F218" s="9" t="inlineStr">
+        <is>
+          <t>دوس على «نسيت الباسورد» في صفحة الدخول، وهيوصلك كود من 6 أرقام على إيميل الحساب: شغال مرة واحدة لمدة 10 دقايق، وليك 5 محاولات بالكتير، وبعدها تعمل باسورد جديد. والفندق عمره ما بيطلب منك الباسورد في تليفون أو شات أو إيميل.</t>
+        </is>
+      </c>
+      <c r="G218" s="9" t="inlineStr">
+        <is>
+          <t>اختر «نسيت كلمة المرور» في صفحة الدخول، فيصلك رمز من 6 أرقام على بريد حسابك: يُستخدم مرة واحدة خلال 10 دقائق، مع 5 محاولات كحد أقصى، ثم تضع كلمة مرور جديدة. ولا يطلب الفندق كلمة المرور أبداً بالهاتف أو المحادثة أو البريد الإلكتروني.</t>
+        </is>
+      </c>
+      <c r="H218" s="12" t="n"/>
+      <c r="I218" s="12" t="n"/>
+      <c r="J218" s="12" t="n"/>
+      <c r="K218" s="12" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="9" t="inlineStr">
+        <is>
+          <t>E218</t>
+        </is>
+      </c>
+      <c r="B219" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C219" s="9" t="inlineStr">
+        <is>
+          <t>INT034</t>
+        </is>
+      </c>
+      <c r="D219" s="9" t="inlineStr">
+        <is>
+          <t>FAQ3996</t>
+        </is>
+      </c>
+      <c r="E219" s="9" t="inlineStr">
+        <is>
+          <t>لازم أعمل حساب عشان أحجز مع المساعد بتاعكم؟</t>
+        </is>
+      </c>
+      <c r="F219" s="9" t="inlineStr">
+        <is>
+          <t>أيوه. من غير لوجين تقدر تسأل أي سؤال عام عن الفندق، لكن الحجز أو إنك تشوف حجز أو تعدّله أو تطلب حاجة محتاج لوجين الأول، وبعدها تقدر تضيف حجز عملته بالتليفون أو من شركة سياحة أو موقع حجز برقمه واسم العيلة اللي عليه. ولو في طوارئ المساعد بيساعدك على طول، عامل لوجين أو لأ.</t>
+        </is>
+      </c>
+      <c r="G219" s="9" t="inlineStr">
+        <is>
+          <t>نعم. دون تسجيل الدخول يمكنك طرح الأسئلة العامة عن الفندق، أما الحجز أو الاطلاع على حجز أو تعديله أو تقديم طلب فيحتاج إلى تسجيل الدخول أولاً، ويمكن بعدها إضافة حجز تم بالهاتف أو عبر وكالة أو منصة حجز برقمه واسم العائلة المسجل عليه. وفي حالات الطوارئ يساعدك المساعد فوراً، سجّلت الدخول أم لا.</t>
+        </is>
+      </c>
+      <c r="H219" s="12" t="n"/>
+      <c r="I219" s="12" t="n"/>
+      <c r="J219" s="12" t="n"/>
+      <c r="K219" s="12" t="n"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K216"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H216" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="H2:H219" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"تمام,محتاج تعديل,مش متأكد"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -14434,7 +14551,7 @@
       </c>
       <c r="B185" s="9" t="inlineStr">
         <is>
-          <t>INT012_F3</t>
+          <t>INT012_F6_visitor_login</t>
         </is>
       </c>
       <c r="C185" s="9" t="n">
@@ -14442,12 +14559,12 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>في مستويات مختلفة في البرنامج؟</t>
+          <t>أنا معايا كام نقطة في برنامج الولاء؟</t>
         </is>
       </c>
       <c r="E185" s="9" t="inlineStr">
         <is>
-          <t>في 4 مستويات: العادي أول ما تشترك، والفضي بعد 10 ليالي، والدهبي بعد 25، والبلاتيني بعد 50 ليلة في السنة.</t>
+          <t>علشان أشوف نقطك لازم تسجّل دخول الأول من موقع الفندق. ولو مش عامل حساب تقدر تعمله بإيميلك، وهيوصلك كود من 6 أرقام تأكّده بيه.</t>
         </is>
       </c>
       <c r="F185" s="12" t="n"/>
@@ -14462,7 +14579,7 @@
       </c>
       <c r="B186" s="9" t="inlineStr">
         <is>
-          <t>INT012_F3</t>
+          <t>INT012_F6_visitor_login</t>
         </is>
       </c>
       <c r="C186" s="9" t="n">
@@ -14470,12 +14587,12 @@
       </c>
       <c r="D186" s="9" t="inlineStr">
         <is>
-          <t>والأعضاء بياخدوا إيه؟</t>
+          <t>ولو نسيت الباسورد؟</t>
         </is>
       </c>
       <c r="E186" s="9" t="inlineStr">
         <is>
-          <t>الفضي: خروج لحد 1 الضهر. الدهبي: لحد 2 الضهر وترقية للأوضة وخصم 10% في السبا. البلاتيني: لحد 4 العصر وفطار ببلاش لاتنين وأولوية في الترقية وخصم 15% في السبا، وكله على حسب المتاح.</t>
+          <t>دوس على «نسيت الباسورد» في صفحة الدخول، وهيوصلك كود على الإيميل شغال 10 دقايق، وبعدها تعمل باسورد جديد.</t>
         </is>
       </c>
       <c r="F186" s="12" t="n"/>
@@ -14490,7 +14607,7 @@
       </c>
       <c r="B187" s="9" t="inlineStr">
         <is>
-          <t>INT012_F3</t>
+          <t>INT012_F6_visitor_login</t>
         </is>
       </c>
       <c r="C187" s="9" t="n">
@@ -14518,7 +14635,7 @@
       </c>
       <c r="B188" s="9" t="inlineStr">
         <is>
-          <t>INT012_F3</t>
+          <t>INT027_F2_discount_request</t>
         </is>
       </c>
       <c r="C188" s="9" t="n">
@@ -14526,12 +14643,12 @@
       </c>
       <c r="D188" s="9" t="inlineStr">
         <is>
-          <t>العضوية مقسمة إزاي؟</t>
+          <t>ممكن تعملولي خصم على الإقامة الجاية؟</t>
         </is>
       </c>
       <c r="E188" s="9" t="inlineStr">
         <is>
-          <t>في 4 مستويات: العادي أول ما تشترك، والفضي بعد 10 ليالي، والدهبي بعد 25، والبلاتيني بعد 50 ليلة في السنة.</t>
+          <t>على السعر المرن أقدر أطبّق خصم الإقامة الطويلة 12% لو 7 ليالي أو أكتر، أو كود خصم ساري. غير كده الفندق هو اللي بيقرر: أقدر أبعت طلب خصم، ولو اتوافق عليه هيوصلك كود شخصي على الإيميل. أبعته؟</t>
         </is>
       </c>
       <c r="F188" s="12" t="n"/>
@@ -14546,7 +14663,7 @@
       </c>
       <c r="B189" s="9" t="inlineStr">
         <is>
-          <t>INT012_F3</t>
+          <t>INT027_F2_discount_request</t>
         </is>
       </c>
       <c r="C189" s="9" t="n">
@@ -14554,12 +14671,12 @@
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>والأعضاء بياخدوا إيه؟</t>
+          <t>آه ياريت، هي 4 ليالي في يناير.</t>
         </is>
       </c>
       <c r="E189" s="9" t="inlineStr">
         <is>
-          <t>الفضي: خروج لحد 1 الضهر. الدهبي: لحد 2 الضهر وترقية للأوضة وخصم 10% في السبا. البلاتيني: لحد 4 العصر وفطار ببلاش لاتنين وأولوية في الترقية وخصم 15% في السبا، وكله على حسب المتاح.</t>
+          <t>تمام، بعت طلب الخصم لـ 4 ليالي في يناير، والرد هيوصلك على الإيميل.</t>
         </is>
       </c>
       <c r="F189" s="12" t="n"/>
@@ -14574,7 +14691,7 @@
       </c>
       <c r="B190" s="9" t="inlineStr">
         <is>
-          <t>INT012_F3</t>
+          <t>INT027_F2_discount_request</t>
         </is>
       </c>
       <c r="C190" s="9" t="n">
@@ -16379,7 +16496,7 @@
       </c>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>كلّم الاستقبال من تليفون الأوضة حالاً، الفندق يقدر يجيب دكتور أو إسعاف. ولو الحالة خطر على الحياة كلّم الطوارئ على طول. انت في أوضة كام؟</t>
+          <t>لو الحالة خطر على الحياة كلّم الإسعاف على 123 حالاً. أنا بلّغت فريق الفندق إن في حالة طوارئ، ورقم الاستقبال ‎+20 2 2794 5500. حضرتك في أوضة كام؟</t>
         </is>
       </c>
       <c r="F254" s="12" t="n"/>
@@ -16407,7 +16524,7 @@
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>الاستقبال اتبلغ بأوضة 1506 والمساعدة جاية في الطريق. وفي إسعافات أولية في الاستقبال.</t>
+          <t>تمام، في حد من الموظفين طالع لأوضة 1506 دلوقتي، والفندق يقدر يجيب دكتور. خليك جنبه وسيب الباب من غير قفل.</t>
         </is>
       </c>
       <c r="F255" s="12" t="n"/>
@@ -16435,7 +16552,7 @@
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>كلّم الاستقبال من تليفون الأوضة حالاً، الفندق يقدر يجيب دكتور أو إسعاف. ولو الحالة خطر على الحياة كلّم الطوارئ على طول. انت في أوضة كام؟</t>
+          <t>لو الحالة خطر على الحياة كلّم الإسعاف على 123 حالاً. أنا بلّغت فريق الفندق إن في حالة طوارئ، ورقم الاستقبال ‎+20 2 2794 5500. حضرتك في أوضة كام؟</t>
         </is>
       </c>
       <c r="F256" s="12" t="n"/>
@@ -16463,7 +16580,7 @@
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>الاستقبال اتبلغ بأوضة 807 والمساعدة جاية في الطريق. وفي إسعافات أولية في الاستقبال.</t>
+          <t>تمام، في حد من الموظفين طالع لأوضة 807 دلوقتي، والفندق يقدر يجيب دكتور. خليك جنبه وسيب الباب من غير قفل.</t>
         </is>
       </c>
       <c r="F257" s="12" t="n"/>
@@ -16491,7 +16608,7 @@
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>كلّم الاستقبال من تليفون الأوضة حالاً، الفندق يقدر يجيب دكتور أو إسعاف. ولو الحالة خطر على الحياة كلّم الطوارئ على طول. انت في أوضة كام؟</t>
+          <t>لو الحالة خطر على الحياة كلّم الإسعاف على 123 حالاً. أنا بلّغت فريق الفندق إن في حالة طوارئ، ورقم الاستقبال ‎+20 2 2794 5500. حضرتك في أوضة كام؟</t>
         </is>
       </c>
       <c r="F258" s="12" t="n"/>
@@ -16519,7 +16636,7 @@
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>الاستقبال اتبلغ بأوضة 1402 والمساعدة جاية في الطريق. وفي إسعافات أولية في الاستقبال.</t>
+          <t>تمام، في حد من الموظفين طالع لأوضة 1402 دلوقتي، والفندق يقدر يجيب دكتور. خليك جنبه وسيب الباب من غير قفل.</t>
         </is>
       </c>
       <c r="F259" s="12" t="n"/>
@@ -16743,7 +16860,7 @@
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>الاستقبال والأمن اتبلغوا بأوضة 1507 وجايين لك. لحد ما ييجوا اقفل الباب واستخدم الخزنة للحاجات الغالية.</t>
+          <t>الاستقبال والأمن اتبلغوا بأوضة 1507 وجايين لك. لحد ما ييجوا اقفل الباب واستخدم الخزنة للحاجات الغالية. وتقدر كمان تبلّغ البوليس على 122.</t>
         </is>
       </c>
       <c r="F267" s="12" t="n"/>
@@ -16799,7 +16916,7 @@
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>الاستقبال والأمن اتبلغوا بأوضة 1407 وجايين لك. لحد ما ييجوا اقفل الباب واستخدم الخزنة للحاجات الغالية.</t>
+          <t>الاستقبال والأمن اتبلغوا بأوضة 1407 وجايين لك. لحد ما ييجوا اقفل الباب واستخدم الخزنة للحاجات الغالية. وتقدر كمان تبلّغ البوليس على 122.</t>
         </is>
       </c>
       <c r="F269" s="12" t="n"/>
@@ -16855,7 +16972,7 @@
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>الاستقبال والأمن اتبلغوا بأوضة 1405 وجايين لك. لحد ما ييجوا اقفل الباب واستخدم الخزنة للحاجات الغالية.</t>
+          <t>الاستقبال والأمن اتبلغوا بأوضة 1405 وجايين لك. لحد ما ييجوا اقفل الباب واستخدم الخزنة للحاجات الغالية. وتقدر كمان تبلّغ البوليس على 122.</t>
         </is>
       </c>
       <c r="F271" s="12" t="n"/>
@@ -17051,7 +17168,7 @@
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>اخرج دلوقتي من مخارج الطوارئ اللي عليها علامات واتبع تعليمات الموظفين. انزل على السلم مش الأسانسير، وروح نقطة التجمع.</t>
+          <t>اخرج دلوقتي من مخارج الطوارئ اللي عليها علامات، وانزل على السلم مش الأسانسير، وروح نقطة التجمع. أنا بلّغت فريق الفندق، ولو شفت نار كلّم المطافي على 180. الاستقبال: ‎+20 2 2794 5500.</t>
         </is>
       </c>
       <c r="F278" s="12" t="n"/>
@@ -17107,7 +17224,7 @@
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>اخرج دلوقتي من مخارج الطوارئ اللي عليها علامات واتبع تعليمات الموظفين. انزل على السلم مش الأسانسير، وروح نقطة التجمع.</t>
+          <t>اخرج دلوقتي من مخارج الطوارئ اللي عليها علامات، وانزل على السلم مش الأسانسير، وروح نقطة التجمع. أنا بلّغت فريق الفندق، ولو شفت نار كلّم المطافي على 180. الاستقبال: ‎+20 2 2794 5500.</t>
         </is>
       </c>
       <c r="F280" s="12" t="n"/>
@@ -17163,7 +17280,7 @@
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>اخرج دلوقتي من مخارج الطوارئ اللي عليها علامات واتبع تعليمات الموظفين. انزل على السلم مش الأسانسير، وروح نقطة التجمع.</t>
+          <t>اخرج دلوقتي من مخارج الطوارئ اللي عليها علامات، وانزل على السلم مش الأسانسير، وروح نقطة التجمع. أنا بلّغت فريق الفندق، ولو شفت نار كلّم المطافي على 180. الاستقبال: ‎+20 2 2794 5500.</t>
         </is>
       </c>
       <c r="F282" s="12" t="n"/>
@@ -19263,7 +19380,7 @@
       </c>
       <c r="E357" s="9" t="inlineStr">
         <is>
-          <t>آسف، ماقدرتش أفهمك صح. وبدل ما أخمن للمرة التالتة هحوّلك لحد من فريق الفندق.</t>
+          <t>أنا آسفة، ماقدرتش أفهم حضرتك صح. وبدل ما أخمّن للمرة التالتة، تحب أوصّلك بحد من فريق الفندق هنا في الشات؟</t>
         </is>
       </c>
       <c r="F357" s="12" t="n"/>
@@ -19286,12 +19403,12 @@
       </c>
       <c r="D358" s="9" t="inlineStr">
         <is>
-          <t>أخيراً. هياخد قد إيه؟</t>
+          <t>أيوه ياريت. هياخد قد إيه؟</t>
         </is>
       </c>
       <c r="E358" s="9" t="inlineStr">
         <is>
-          <t>الاستقبال موجود 24 ساعة، فيه حد متاح دلوقتي. ولو مش عايز تستنى هنا تقدر تكلم الاستقبال على طول وهيكون معاهم تفاصيل المحادثة دي.</t>
+          <t>في حد من الموظفين بيدخل الشات دلوقتي وهيشوف كلامنا من الأول، فمش هتحتاج تعيد حاجة.</t>
         </is>
       </c>
       <c r="F358" s="12" t="n"/>
